--- a/SLPSO/DRLPSO_CEC2021_先前的数据/Analyze_of_bound/changing_upperbound/comparison_results_upperbound.xlsx
+++ b/SLPSO/DRLPSO_CEC2021_先前的数据/Analyze_of_bound/changing_upperbound/comparison_results_upperbound.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.41E-219±0.00E+00 (≈)</t>
+          <t>3.41E-219±0.00E+00 (+)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.26E+00±4.68E+00 (≈)</t>
+          <t>9.26E+00±4.68E+00 (+)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.51E+00±4.56E+00 (≈)</t>
+          <t>9.51E+00±4.56E+00 (+)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.23E+01±6.09E+01 (≈)</t>
+          <t>4.23E+01±6.09E+01 (-)</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.16E+00±5.19E+00 (≈)</t>
+          <t>2.16E+00±5.19E+00 (-)</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.56E+01±4.29E+01 (≈)</t>
+          <t>2.56E+01±4.29E+01 (-)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.46E+01±5.83E+01 (≈)</t>
+          <t>3.46E+01±5.83E+01 (-)</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.00E+00±0.00E+00 (≈)</t>
+          <t>0.00E+00±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.82E+01±1.42E-01 (≈)</t>
+          <t>4.82E+01±1.42E-01 (+)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -844,27 +844,27 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1/8/1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2/8/0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>0/10/0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0/10/0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0/10/0</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0/10/0</t>
+          <t>1/8/1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/9/0</t>
+          <t>1/6/3</t>
         </is>
       </c>
     </row>

--- a/SLPSO/DRLPSO_CEC2021_先前的数据/Analyze_of_bound/changing_upperbound/comparison_results_upperbound.xlsx
+++ b/SLPSO/DRLPSO_CEC2021_先前的数据/Analyze_of_bound/changing_upperbound/comparison_results_upperbound.xlsx
@@ -478,27 +478,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.41E-219±0.00E+00 (+)</t>
+          <t>3.41E-219±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.14E-219±0.00E+00 (≈)</t>
+          <t>1.14E-219±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.31E-222±0.00E+00 (≈)</t>
+          <t>2.31E-222±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.63E-222±0.00E+00 (≈)</t>
+          <t>3.63E-222±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.16E-222±0.00E+00 (≈)</t>
+          <t>1.16E-222±0.00E+00 (-)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.05E+01±8.08E+01 (≈)</t>
+          <t>6.05E+01±8.08E+01 (-)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.46E+01±7.07E+01 (≈)</t>
+          <t>4.46E+01±7.07E+01 (-)</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.26E+00±4.68E+00 (+)</t>
+          <t>9.26E+00±4.68E+00 (≈)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.51E+00±4.56E+00 (+)</t>
+          <t>9.51E+00±4.56E+00 (≈)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -668,17 +668,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.25E+00±4.26E+00 (≈)</t>
+          <t>2.25E+00±4.26E+00 (-)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6.15E+00±2.36E+01 (≈)</t>
+          <t>6.15E+00±2.36E+01 (-)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5.85E+00±2.19E+01 (≈)</t>
+          <t>5.85E+00±2.19E+01 (-)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.71E+01±6.64E+01 (≈)</t>
+          <t>5.71E+01±6.64E+01 (+)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.46E+01±5.83E+01 (-)</t>
+          <t>3.46E+01±5.83E+01 (≈)</t>
         </is>
       </c>
     </row>
@@ -737,17 +737,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30E-01±1.81E+00 (≈)</t>
+          <t>3.30E-01±1.81E+00 (-)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.21E-01±2.75E+00 (≈)</t>
+          <t>7.21E-01±2.75E+00 (+)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.77E-01±2.58E+00 (≈)</t>
+          <t>6.77E-01±2.58E+00 (-)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.67E-01±2.92E+00 (≈)</t>
+          <t>7.67E-01±2.92E+00 (+)</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.81E+01±1.81E-01 (≈)</t>
+          <t>4.81E+01±1.81E-01 (+)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.92E+01±5.65E+00 (≈)</t>
+          <t>4.92E+01±5.65E+00 (+)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -844,27 +844,27 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1/8/1</t>
+          <t>1/6/3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2/8/0</t>
+          <t>2/5/3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0/10/0</t>
+          <t>1/6/3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1/8/1</t>
+          <t>1/6/3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/6/3</t>
+          <t>2/4/4</t>
         </is>
       </c>
     </row>
